--- a/Requisitos Funcionais/ES2N-Requisitos Funcionais v4.0.xlsx
+++ b/Requisitos Funcionais/ES2N-Requisitos Funcionais v4.0.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toyotabrasil-my.sharepoint.com/personal/aaloliveira_toyota_com_br/Documents/Documentos/GitHub/deploynasexta/Requisitos Funcionais/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_26AEB4EC332602B7D99C5FBD30863A8819128564" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{808E047F-E561-43C9-B7DC-2F92F1C33063}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -76,9 +95,6 @@
     <t>Usuário interno</t>
   </si>
   <si>
-    <t>Pode executar os requisitos RF01 e RF03 a RF14.</t>
-  </si>
-  <si>
     <t>RF03</t>
   </si>
   <si>
@@ -251,13 +267,16 @@
   </si>
   <si>
     <t>O sistema deve permitir cadastrar, alterar, consultar e inativar categorias de itens utilizados no controle de estoque,por exemplo, arroz, feijão, maca, lençois, dipirona, etc.</t>
+  </si>
+  <si>
+    <t>Pode executar os requisitos RF05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +421,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -694,26 +721,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+    <col min="2" max="2" width="64.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="78" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="46.26953125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -723,30 +750,30 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+    <row r="3" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="21" customHeight="1">
+    <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
+    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="78" customHeight="1">
+    <row r="9" spans="1:6" s="4" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
@@ -766,7 +793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="69.75">
+    <row r="10" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
@@ -786,27 +813,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="69.75">
+    <row r="11" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" ht="69.75">
+    <row r="12" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>17</v>
@@ -821,18 +848,18 @@
         <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="46.5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="47" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>19</v>
@@ -841,250 +868,250 @@
         <v>14</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69.75">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="93">
+    </row>
+    <row r="15" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="93">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="93">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="69.75">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="72" customHeight="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="69.75">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="93">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="93">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" ht="116.25">
+    <row r="23" spans="1:6" ht="117.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="93">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="72" customHeight="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="36" customHeight="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1098,5 +1125,8 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 •• PROTECTED 関係者外秘&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Requisitos Funcionais/ES2N-Requisitos Funcionais v4.0.xlsx
+++ b/Requisitos Funcionais/ES2N-Requisitos Funcionais v4.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://toyotabrasil-my.sharepoint.com/personal/aaloliveira_toyota_com_br/Documents/Documentos/GitHub/deploynasexta/Requisitos Funcionais/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_26AEB4EC332602B7D99C5FBD30863A8819128564" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{808E047F-E561-43C9-B7DC-2F92F1C33063}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_26AEB4EC332602B7D99C5FBD30863A8819128564" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DEC2327-C7AC-4D2E-A69F-25DFFD25E375}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t xml:space="preserve">LISTA DE REQUISITOS FUNCIONAIS </t>
   </si>
@@ -80,9 +80,6 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Depende do requisito RF02.</t>
-  </si>
-  <si>
     <t>RF02</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>O sistema deve permitir que o usuário interno encerre sua sessão de uso de forma segura.</t>
   </si>
   <si>
-    <t>Encerra a sessão iniciada pelo requisito RF02.</t>
-  </si>
-  <si>
     <t>RF04</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
     <t>Média</t>
   </si>
   <si>
-    <t>Pode ser executado a partir do requisito RF02.</t>
-  </si>
-  <si>
     <t>RF05</t>
   </si>
   <si>
@@ -134,9 +125,6 @@
     <t>Administrador e Colaborador</t>
   </si>
   <si>
-    <t>Pode apoiar a execução do requisito RF06.</t>
-  </si>
-  <si>
     <t>RF06</t>
   </si>
   <si>
@@ -146,9 +134,6 @@
     <t>O sistema deve permitir cadastrar, alterar, consultar e cancelar solicitações de retirada de doações, registrando data, período do dia, endereço, item a ser doado e responsável pelo atendimento.</t>
   </si>
   <si>
-    <t>Pode executar o requisito RF07.</t>
-  </si>
-  <si>
     <t>RF07</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
     <t>O sistema deve permitir registrar entradas e saídas de itens no estoque a partir do recebimento de doações e da distribuição de itens, mantendo o saldo atualizado.</t>
   </si>
   <si>
-    <t>Atualiza informações utilizadas nos requisitos RF08, RF09 e RF14.</t>
-  </si>
-  <si>
     <t>RF08</t>
   </si>
   <si>
@@ -170,9 +152,6 @@
     <t>O sistema deve permitir consultar o estoque com pesquisa e filtragem por nome do item, categoria, validade e disponibilidade.</t>
   </si>
   <si>
-    <t>Pode apoiar a execução dos requisitos RF06, RF07, RF09 e RF14.</t>
-  </si>
-  <si>
     <t>RF09</t>
   </si>
   <si>
@@ -182,18 +161,12 @@
     <t>O sistema deve permitir gerar relatórios de doações recebidas, movimentação de estoque e itens próximos do vencimento, com filtro por período.</t>
   </si>
   <si>
-    <t>Utiliza dados dos requisitos RF05 a RF08 e RF10 a RF13.</t>
-  </si>
-  <si>
     <t>RF10</t>
   </si>
   <si>
     <t>Gerenciar categorias</t>
   </si>
   <si>
-    <t>Pode ser executado antes dos requisitos RF11 e RF12.</t>
-  </si>
-  <si>
     <t>RF11</t>
   </si>
   <si>
@@ -218,9 +191,6 @@
     <t>Sistema</t>
   </si>
   <si>
-    <t>Pode apoiar a execução dos requisitos RF08, RF09 e RF14.</t>
-  </si>
-  <si>
     <t>RF14</t>
   </si>
   <si>
@@ -228,9 +198,6 @@
   </si>
   <si>
     <t>O sistema deve apresentar um painel com indicadores de doações recebidas, movimentação de estoque, itens próximos do vencimento e doadores ativos.</t>
-  </si>
-  <si>
-    <t>Utiliza dados consolidados dos requisitos RF05 a RF13.</t>
   </si>
   <si>
     <t>*** Observação: o termo 'Gerenciar' é utilizado quando o requisito contempla operações de consulta, cadastro, alteração e inativação/exclusão lógica, conforme orientação da professora.</t>
@@ -759,7 +726,7 @@
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1"/>
     </row>
@@ -809,240 +776,220 @@
       <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="E12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="47" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="D13" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>33</v>
-      </c>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>41</v>
-      </c>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>65</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>52</v>
-      </c>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>14</v>
@@ -1051,67 +998,61 @@
     </row>
     <row r="23" spans="1:6" ht="117.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" ht="94" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>37</v>
-      </c>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="F25" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
